--- a/Data/FlightPlan/FPL_13AUG26.xlsx
+++ b/Data/FlightPlan/FPL_13AUG26.xlsx
@@ -731,6 +731,9 @@
     <t>08:15</t>
   </si>
   <si>
+    <t>10:18</t>
+  </si>
+  <si>
     <t>10:55</t>
   </si>
   <si>
@@ -749,6 +752,12 @@
     <t>16:55</t>
   </si>
   <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
     <t>19:55</t>
   </si>
   <si>
@@ -758,6 +767,9 @@
     <t>00:05</t>
   </si>
   <si>
+    <t>00:40</t>
+  </si>
+  <si>
     <t>VN-A551</t>
   </si>
   <si>
@@ -869,9 +881,6 @@
     <t>15:35</t>
   </si>
   <si>
-    <t>00:40</t>
-  </si>
-  <si>
     <t>VN-A607</t>
   </si>
   <si>
@@ -893,9 +902,6 @@
     <t>KUL</t>
   </si>
   <si>
-    <t>18:05</t>
-  </si>
-  <si>
     <t>23:45</t>
   </si>
   <si>
@@ -965,9 +971,6 @@
     <t>BKK</t>
   </si>
   <si>
-    <t>15:45</t>
-  </si>
-  <si>
     <t>16:45</t>
   </si>
   <si>
@@ -1031,6 +1034,9 @@
     <t>VN-A643</t>
   </si>
   <si>
+    <t>12:36</t>
+  </si>
+  <si>
     <t>13:45</t>
   </si>
   <si>
@@ -1214,6 +1220,9 @@
     <t>10:05</t>
   </si>
   <si>
+    <t>10:22</t>
+  </si>
+  <si>
     <t>VN-A672</t>
   </si>
   <si>
@@ -1394,7 +1403,7 @@
     <t>Total Record(s): 411</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 13, 2026 08:59</t>
+    <t xml:space="preserve">Generated on  Aug 13, 2026 09:07</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -6202,7 +6211,7 @@
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
-        <v>229</v>
+        <v>240</v>
       </c>
     </row>
     <row r="147" ht="14.25" customHeight="1">
@@ -6235,7 +6244,7 @@
         <v>95</v>
       </c>
       <c t="s" r="K147" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
@@ -6272,11 +6281,11 @@
         <v>222</v>
       </c>
       <c t="s" r="K148" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6300,17 +6309,21 @@
         <v>27</v>
       </c>
       <c t="s" r="H149" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>245</v>
-      </c>
-      <c r="K149" s="7"/>
+        <v>246</v>
+      </c>
+      <c t="s" r="K149" s="7">
+        <v>247</v>
+      </c>
       <c r="L149" s="7"/>
-      <c r="M149" s="7"/>
+      <c t="s" r="M149" s="7">
+        <v>233</v>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c t="s" r="A150" s="6">
@@ -6330,7 +6343,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H150" s="8">
         <v>27</v>
@@ -6341,9 +6354,13 @@
       <c t="s" r="J150" s="7">
         <v>183</v>
       </c>
-      <c r="K150" s="7"/>
+      <c t="s" r="K150" s="7">
+        <v>248</v>
+      </c>
       <c r="L150" s="7"/>
-      <c r="M150" s="7"/>
+      <c t="s" r="M150" s="7">
+        <v>64</v>
+      </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
       <c t="s" r="A151" s="6">
@@ -6369,14 +6386,18 @@
         <v>101</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>132</v>
       </c>
-      <c r="K151" s="7"/>
+      <c t="s" r="K151" s="7">
+        <v>172</v>
+      </c>
       <c r="L151" s="7"/>
-      <c r="M151" s="7"/>
+      <c t="s" r="M151" s="7">
+        <v>250</v>
+      </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
       <c t="s" r="A152" s="6">
@@ -6402,14 +6423,18 @@
         <v>27</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>248</v>
-      </c>
-      <c r="K152" s="7"/>
+        <v>251</v>
+      </c>
+      <c t="s" r="K152" s="7">
+        <v>113</v>
+      </c>
       <c r="L152" s="7"/>
-      <c r="M152" s="7"/>
+      <c t="s" r="M152" s="7">
+        <v>252</v>
+      </c>
     </row>
     <row r="153" ht="14.25" customHeight="1">
       <c r="A153" s="6"/>
@@ -6438,7 +6463,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6458,7 +6483,7 @@
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6473,7 +6498,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6506,7 +6531,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6515,13 +6540,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H156" s="8">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6539,13 +6564,13 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>27</v>
@@ -6554,7 +6579,7 @@
         <v>203</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6587,7 +6612,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6599,7 +6624,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>221</v>
@@ -6624,7 +6649,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6636,10 +6661,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6672,7 +6697,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6684,15 +6709,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6707,7 +6732,7 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
@@ -6716,7 +6741,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="I163" s="7">
         <v>123</v>
@@ -6727,7 +6752,7 @@
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c t="s" r="M163" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="164" ht="14.25" customHeight="1">
@@ -6742,19 +6767,19 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>24</v>
@@ -6775,7 +6800,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6787,7 +6812,7 @@
         <v>65</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c t="s" r="J165" s="7">
         <v>87</v>
@@ -6823,13 +6848,13 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="H167" s="8">
         <v>27</v>
@@ -6843,7 +6868,7 @@
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -6858,7 +6883,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6891,7 +6916,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6924,7 +6949,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6933,13 +6958,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>173</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6972,7 +6997,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6987,12 +7012,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7007,7 +7032,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7016,13 +7041,13 @@
         <v>45</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -7040,19 +7065,19 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>45</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J174" s="7">
         <v>201</v>
@@ -7073,7 +7098,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7106,7 +7131,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7121,7 +7146,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7154,7 +7179,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7189,7 +7214,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7201,10 +7226,10 @@
         <v>136</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7222,7 +7247,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7237,7 +7262,7 @@
         <v>232</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7255,7 +7280,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7264,10 +7289,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>85</v>
@@ -7288,13 +7313,13 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>16</v>
@@ -7303,7 +7328,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7336,7 +7361,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7348,17 +7373,17 @@
         <v>45</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c t="s" r="K184" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="L184" s="7"/>
       <c t="s" r="M184" s="7">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="185" ht="15" customHeight="1">
@@ -7373,7 +7398,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7385,7 +7410,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>198</v>
@@ -7406,7 +7431,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7421,7 +7446,7 @@
         <v>222</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7439,7 +7464,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7454,7 +7479,7 @@
         <v>121</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7472,7 +7497,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7484,7 +7509,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>286</v>
+        <v>252</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>34</v>
@@ -7520,7 +7545,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7540,7 +7565,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -7555,7 +7580,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7564,13 +7589,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="I191" s="7">
         <v>187</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7588,22 +7613,22 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7636,7 +7661,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7645,7 +7670,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="I194" s="7">
         <v>20</v>
@@ -7669,13 +7694,13 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>16</v>
@@ -7702,7 +7727,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7714,10 +7739,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7735,7 +7760,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7768,7 +7793,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7780,7 +7805,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>237</v>
@@ -7816,7 +7841,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7828,7 +7853,7 @@
         <v>215</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>51</v>
@@ -7849,7 +7874,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7861,10 +7886,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7882,7 +7907,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7894,7 +7919,7 @@
         <v>225</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>126</v>
@@ -7930,7 +7955,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7950,7 +7975,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -7965,7 +7990,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7977,7 +8002,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>167</v>
@@ -7998,7 +8023,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8013,7 +8038,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8031,7 +8056,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8046,7 +8071,7 @@
         <v>222</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -8064,7 +8089,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8112,7 +8137,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8124,7 +8149,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>158</v>
@@ -8132,7 +8157,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8147,7 +8172,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8180,7 +8205,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8213,7 +8238,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8225,10 +8250,10 @@
         <v>225</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8261,7 +8286,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8273,15 +8298,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8296,7 +8321,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8329,7 +8354,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8362,7 +8387,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8395,7 +8420,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8428,7 +8453,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8476,7 +8501,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8491,12 +8516,12 @@
         <v>74</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8511,7 +8536,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8531,7 +8556,7 @@
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8546,7 +8571,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8555,10 +8580,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>61</v>
@@ -8579,13 +8604,13 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>16</v>
@@ -8594,7 +8619,7 @@
         <v>159</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8612,7 +8637,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8645,7 +8670,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8660,7 +8685,7 @@
         <v>223</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8693,7 +8718,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8728,7 +8753,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8763,7 +8788,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8772,10 +8797,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>51</v>
@@ -8796,19 +8821,19 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>231</v>
@@ -8829,7 +8854,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8838,16 +8863,16 @@
         <v>27</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>318</v>
+        <v>247</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>54</v>
       </c>
       <c t="s" r="K233" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
@@ -8866,13 +8891,13 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>27</v>
@@ -8884,7 +8909,7 @@
         <v>172</v>
       </c>
       <c t="s" r="K234" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="L234" s="7"/>
       <c t="s" r="M234" s="7">
@@ -8918,7 +8943,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8951,7 +8976,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8960,13 +8985,13 @@
         <v>136</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="I237" s="7">
         <v>141</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8984,19 +9009,19 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="H238" s="8">
         <v>136</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>24</v>
@@ -9017,7 +9042,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9050,7 +9075,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9062,7 +9087,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>235</v>
@@ -9098,7 +9123,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9110,7 +9135,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J242" s="7">
         <v>80</v>
@@ -9118,7 +9143,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9133,7 +9158,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9166,7 +9191,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9178,7 +9203,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>72</v>
@@ -9199,7 +9224,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9208,13 +9233,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9232,22 +9257,22 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G246" s="8">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="H246" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9280,7 +9305,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9295,12 +9320,12 @@
         <v>237</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9315,7 +9340,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9330,12 +9355,12 @@
         <v>123</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9350,7 +9375,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9359,7 +9384,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>108</v>
@@ -9383,13 +9408,13 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>17</v>
@@ -9398,7 +9423,7 @@
         <v>231</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9416,7 +9441,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9425,13 +9450,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9449,22 +9474,22 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9497,7 +9522,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9516,7 +9541,9 @@
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
-      <c r="M255" s="7"/>
+      <c t="s" r="M255" s="7">
+        <v>341</v>
+      </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
       <c t="s" r="A256" s="6">
@@ -9530,7 +9557,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9545,7 +9572,7 @@
         <v>70</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9563,7 +9590,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9575,7 +9602,7 @@
         <v>125</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>318</v>
+        <v>247</v>
       </c>
       <c t="s" r="J257" s="7">
         <v>234</v>
@@ -9596,7 +9623,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9629,7 +9656,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9641,7 +9668,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>156</v>
@@ -9677,7 +9704,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9692,7 +9719,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
@@ -9712,7 +9739,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9727,7 +9754,7 @@
         <v>208</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9745,7 +9772,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9760,7 +9787,7 @@
         <v>159</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9778,7 +9805,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9787,7 +9814,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="I264" s="7">
         <v>86</v>
@@ -9826,7 +9853,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9838,7 +9865,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="J266" s="7">
         <v>19</v>
@@ -9846,7 +9873,7 @@
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -9861,7 +9888,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9870,10 +9897,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>232</v>
@@ -9894,13 +9921,13 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>27</v>
@@ -9927,7 +9954,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9975,7 +10002,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9987,7 +10014,7 @@
         <v>125</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>168</v>
@@ -10008,7 +10035,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10020,7 +10047,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>187</v>
@@ -10041,7 +10068,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10074,7 +10101,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10107,7 +10134,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10155,7 +10182,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10167,14 +10194,16 @@
         <v>45</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>198</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
-      <c r="M277" s="7"/>
+      <c t="s" r="M277" s="7">
+        <v>241</v>
+      </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
       <c t="s" r="A278" s="6">
@@ -10188,7 +10217,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10221,7 +10250,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10230,7 +10259,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>38</v>
@@ -10254,13 +10283,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>27</v>
@@ -10283,11 +10312,11 @@
         <v>31</v>
       </c>
       <c t="s" r="C281" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10296,13 +10325,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10335,7 +10364,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10347,7 +10376,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="J283" s="7">
         <v>126</v>
@@ -10355,7 +10384,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10370,7 +10399,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10390,7 +10419,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10405,7 +10434,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10420,7 +10449,7 @@
         <v>53</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10438,7 +10467,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10453,7 +10482,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10471,7 +10500,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10504,7 +10533,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10516,10 +10545,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10552,7 +10581,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10567,12 +10596,12 @@
         <v>126</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10587,7 +10616,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
@@ -10599,7 +10628,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>198</v>
@@ -10620,7 +10649,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10653,7 +10682,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
@@ -10662,7 +10691,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>84</v>
@@ -10686,13 +10715,13 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>16</v>
@@ -10719,7 +10748,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10752,7 +10781,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -10764,10 +10793,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10800,7 +10829,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10812,15 +10841,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -10835,7 +10864,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10870,7 +10899,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10885,7 +10914,7 @@
         <v>57</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10903,7 +10932,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10915,7 +10944,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>141</v>
@@ -10936,7 +10965,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10969,7 +10998,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11002,7 +11031,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11035,7 +11064,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11047,7 +11076,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>174</v>
@@ -11083,7 +11112,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11103,7 +11132,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11118,7 +11147,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11151,7 +11180,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11160,13 +11189,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>232</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11184,13 +11213,13 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>16</v>
@@ -11232,7 +11261,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11241,18 +11270,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11267,13 +11296,13 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>16</v>
@@ -11287,7 +11316,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11302,7 +11331,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11311,13 +11340,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11335,19 +11364,19 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>209</v>
@@ -11368,7 +11397,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11401,7 +11430,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11410,13 +11439,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>144</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>294</v>
+        <v>248</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11434,22 +11463,22 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11482,7 +11511,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11494,10 +11523,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11517,7 +11546,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11537,7 +11566,7 @@
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11552,7 +11581,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11585,7 +11614,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11618,7 +11647,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11627,10 +11656,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>143</v>
@@ -11651,22 +11680,22 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>318</v>
+        <v>247</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11684,7 +11713,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11696,7 +11725,7 @@
         <v>106</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>64</v>
@@ -11717,7 +11746,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11765,7 +11794,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
@@ -11798,7 +11827,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -11807,7 +11836,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="I330" s="7">
         <v>70</v>
@@ -11831,13 +11860,13 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>16</v>
@@ -11879,7 +11908,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11888,13 +11917,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="I333" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11912,13 +11941,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>16</v>
@@ -11945,7 +11974,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11954,10 +11983,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>223</v>
@@ -11978,19 +12007,19 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J336" s="7">
         <v>31</v>
@@ -12011,7 +12040,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12020,10 +12049,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>190</v>
@@ -12044,22 +12073,22 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12092,7 +12121,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12104,7 +12133,7 @@
         <v>89</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>78</v>
@@ -12127,7 +12156,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12147,7 +12176,7 @@
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12162,7 +12191,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12195,7 +12224,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12204,13 +12233,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12228,13 +12257,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>27</v>
@@ -12276,7 +12305,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12288,15 +12317,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12311,7 +12340,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12344,7 +12373,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12353,7 +12382,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="I348" s="7">
         <v>51</v>
@@ -12377,13 +12406,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>27</v>
@@ -12392,7 +12421,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12410,7 +12439,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12443,7 +12472,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12455,7 +12484,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>112</v>
@@ -12491,7 +12520,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12500,7 +12529,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="I353" s="7">
         <v>139</v>
@@ -12526,13 +12555,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>27</v>
@@ -12559,7 +12588,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -12592,7 +12621,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12607,7 +12636,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12625,7 +12654,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12640,7 +12669,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12673,7 +12702,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12682,10 +12711,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>90</v>
@@ -12693,7 +12722,7 @@
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -12708,27 +12737,27 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>169</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -12743,7 +12772,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -12752,13 +12781,13 @@
         <v>169</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12776,19 +12805,19 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="H362" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>51</v>
@@ -12809,7 +12838,7 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
@@ -12818,10 +12847,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>231</v>
@@ -12842,13 +12871,13 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="H364" s="8">
         <v>16</v>
@@ -12875,7 +12904,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12908,7 +12937,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12923,7 +12952,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12956,7 +12985,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -12968,7 +12997,7 @@
         <v>146</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>79</v>
@@ -12976,7 +13005,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -12991,7 +13020,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13003,7 +13032,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J369" s="7">
         <v>127</v>
@@ -13026,7 +13055,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13041,7 +13070,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13059,7 +13088,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13092,7 +13121,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -13101,10 +13130,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c t="s" r="J372" s="7">
         <v>213</v>
@@ -13125,19 +13154,19 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>227</v>
@@ -13173,7 +13202,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13185,14 +13214,16 @@
         <v>27</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>198</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
-      <c r="M375" s="7"/>
+      <c t="s" r="M375" s="7">
+        <v>304</v>
+      </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
       <c t="s" r="A376" s="6">
@@ -13206,7 +13237,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13239,7 +13270,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13272,7 +13303,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13320,13 +13351,13 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>27</v>
@@ -13342,7 +13373,7 @@
       </c>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -13357,7 +13388,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13390,7 +13421,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13423,7 +13454,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
@@ -13438,7 +13469,7 @@
         <v>54</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13456,7 +13487,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -13489,7 +13520,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -13537,7 +13568,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13546,17 +13577,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
-      <c r="M387" s="7"/>
+      <c t="s" r="M387" s="7">
+        <v>403</v>
+      </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
       <c t="s" r="A388" s="6">
@@ -13570,13 +13603,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>16</v>
@@ -13603,7 +13636,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
@@ -13612,10 +13645,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H389" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>117</v>
@@ -13636,13 +13669,13 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G390" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="H390" s="8">
         <v>16</v>
@@ -13669,7 +13702,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
@@ -13678,7 +13711,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>201</v>
@@ -13702,13 +13735,13 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>16</v>
@@ -13750,13 +13783,13 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F394" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>27</v>
@@ -13765,12 +13798,12 @@
         <v>25</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -13785,7 +13818,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
@@ -13797,7 +13830,7 @@
         <v>178</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>118</v>
@@ -13818,7 +13851,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13851,7 +13884,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13866,7 +13899,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13899,7 +13932,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13934,7 +13967,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -13967,7 +14000,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -13982,7 +14015,7 @@
         <v>130</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14000,7 +14033,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14033,7 +14066,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
@@ -14048,7 +14081,7 @@
         <v>132</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -14066,7 +14099,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14078,10 +14111,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14114,7 +14147,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F406" s="7">
         <v>321</v>
@@ -14149,7 +14182,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14158,7 +14191,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H407" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="I407" s="7">
         <v>199</v>
@@ -14182,13 +14215,13 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>27</v>
@@ -14215,7 +14248,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14224,13 +14257,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c t="s" r="I409" s="7">
         <v>40</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14248,22 +14281,22 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14296,7 +14329,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F412" s="7">
         <v>320</v>
@@ -14316,7 +14349,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14331,7 +14364,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14364,7 +14397,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -14379,7 +14412,7 @@
         <v>51</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14397,7 +14430,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -14409,7 +14442,7 @@
         <v>106</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>118</v>
@@ -14430,7 +14463,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -14442,7 +14475,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>171</v>
@@ -14463,7 +14496,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -14472,10 +14505,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>176</v>
@@ -14496,13 +14529,13 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>27</v>
@@ -14511,7 +14544,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14544,7 +14577,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F420" s="7">
         <v>320</v>
@@ -14556,7 +14589,7 @@
         <v>178</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c t="s" r="J420" s="7">
         <v>206</v>
@@ -14564,7 +14597,7 @@
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -14579,7 +14612,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -14599,7 +14632,7 @@
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -14614,7 +14647,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -14626,7 +14659,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c t="s" r="J422" s="7">
         <v>61</v>
@@ -14647,7 +14680,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14662,7 +14695,7 @@
         <v>109</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14680,7 +14713,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14692,7 +14725,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>28</v>
@@ -14713,7 +14746,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -14746,7 +14779,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -14755,13 +14788,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H426" s="8">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c t="s" r="I426" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -14779,22 +14812,22 @@
       </c>
       <c r="D427" s="7"/>
       <c t="s" r="E427" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F427" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G427" s="8">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c t="s" r="H427" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I427" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c t="s" r="J427" s="7">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="K427" s="7"/>
       <c r="L427" s="7"/>
@@ -14827,7 +14860,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -14839,10 +14872,10 @@
         <v>149</v>
       </c>
       <c t="s" r="I429" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
@@ -14860,7 +14893,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -14875,7 +14908,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -14893,7 +14926,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -14926,7 +14959,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -14959,7 +14992,7 @@
       </c>
       <c r="D433" s="7"/>
       <c t="s" r="E433" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="F433" s="7">
         <v>321</v>
@@ -14974,7 +15007,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J433" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K433" s="7"/>
       <c r="L433" s="7"/>
@@ -15007,7 +15040,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -15016,10 +15049,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H435" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>221</v>
@@ -15027,7 +15060,7 @@
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -15042,13 +15075,13 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G436" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="H436" s="8">
         <v>16</v>
@@ -15075,7 +15108,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -15084,13 +15117,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H437" s="8">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c t="s" r="I437" s="7">
         <v>217</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15108,22 +15141,22 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G438" s="8">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c t="s" r="H438" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c t="s" r="J438" s="7">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K438" s="7"/>
       <c r="L438" s="7"/>
@@ -15156,7 +15189,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -15176,7 +15209,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15191,7 +15224,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -15203,7 +15236,7 @@
         <v>169</v>
       </c>
       <c t="s" r="I441" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J441" s="7">
         <v>59</v>
@@ -15224,7 +15257,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -15257,7 +15290,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -15269,7 +15302,7 @@
         <v>178</v>
       </c>
       <c t="s" r="I443" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="J443" s="7">
         <v>26</v>
@@ -15290,7 +15323,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -15305,7 +15338,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J444" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K444" s="7"/>
       <c r="L444" s="7"/>
@@ -15323,7 +15356,7 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
@@ -15335,7 +15368,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c t="s" r="J445" s="7">
         <v>139</v>
@@ -15371,7 +15404,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15383,7 +15416,7 @@
         <v>169</v>
       </c>
       <c t="s" r="I447" s="7">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c t="s" r="J447" s="7">
         <v>150</v>
@@ -15391,7 +15424,7 @@
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -15406,7 +15439,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15441,7 +15474,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15450,18 +15483,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H449" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="I449" s="7">
         <v>129</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -15476,13 +15509,13 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G450" s="8">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="H450" s="8">
         <v>16</v>
@@ -15509,7 +15542,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
@@ -15542,7 +15575,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F452" s="7">
         <v>321</v>
@@ -15554,7 +15587,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I452" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c t="s" r="J452" s="7">
         <v>40</v>
@@ -15575,7 +15608,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F453" s="7">
         <v>321</v>
@@ -15584,13 +15617,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="I453" s="7">
         <v>155</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15608,19 +15641,19 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F454" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c t="s" r="J454" s="7">
         <v>98</v>
@@ -15656,7 +15689,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
@@ -15675,7 +15708,9 @@
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
-      <c r="M456" s="7"/>
+      <c t="s" r="M456" s="7">
+        <v>127</v>
+      </c>
     </row>
     <row r="457" ht="14.25" customHeight="1">
       <c t="s" r="A457" s="6">
@@ -15689,7 +15724,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -15701,10 +15736,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15722,7 +15757,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
@@ -15731,13 +15766,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H458" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="I458" s="7">
         <v>222</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>318</v>
+        <v>247</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -15755,13 +15790,13 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G459" s="8">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="H459" s="8">
         <v>16</v>
@@ -15788,7 +15823,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F460" s="7">
         <v>320</v>
@@ -15797,7 +15832,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H460" s="8">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c t="s" r="I460" s="7">
         <v>30</v>
@@ -15821,13 +15856,13 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F461" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G461" s="8">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c t="s" r="H461" s="8">
         <v>16</v>
@@ -15836,7 +15871,7 @@
         <v>66</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15869,7 +15904,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -15881,7 +15916,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J463" s="7">
         <v>50</v>
@@ -15889,7 +15924,7 @@
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -15904,7 +15939,7 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
@@ -15919,7 +15954,7 @@
         <v>216</v>
       </c>
       <c t="s" r="J464" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
@@ -15937,7 +15972,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -15970,7 +16005,7 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
@@ -16018,7 +16053,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -16030,7 +16065,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J468" s="7">
         <v>209</v>
@@ -16051,7 +16086,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
@@ -16063,7 +16098,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I469" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J469" s="7">
         <v>222</v>
@@ -16084,7 +16119,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -16117,7 +16152,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="F471" s="7">
         <v>321</v>
@@ -16129,10 +16164,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J471" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
@@ -16165,7 +16200,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F473" s="7">
         <v>320</v>
@@ -16177,7 +16212,7 @@
         <v>101</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J473" s="7">
         <v>91</v>
@@ -16185,7 +16220,7 @@
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
       <c t="s" r="M473" s="7">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="474" ht="14.25" customHeight="1">
@@ -16200,7 +16235,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F474" s="7">
         <v>320</v>
@@ -16218,11 +16253,11 @@
         <v>129</v>
       </c>
       <c t="s" r="K474" s="7">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="L474" s="7"/>
       <c t="s" r="M474" s="7">
-        <v>241</v>
+        <v>129</v>
       </c>
     </row>
     <row r="475" ht="15" customHeight="1">
@@ -16237,7 +16272,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F475" s="7">
         <v>320</v>
@@ -16246,10 +16281,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H475" s="8">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="J475" s="7">
         <v>62</v>
@@ -16270,13 +16305,13 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F476" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G476" s="8">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c t="s" r="H476" s="8">
         <v>27</v>
@@ -16318,7 +16353,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F478" s="7">
         <v>330</v>
@@ -16351,7 +16386,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
@@ -16360,7 +16395,7 @@
         <v>101</v>
       </c>
       <c t="s" r="H479" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="I479" s="7">
         <v>209</v>
@@ -16384,13 +16419,13 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F480" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G480" s="8">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c t="s" r="H480" s="8">
         <v>101</v>
@@ -16432,7 +16467,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F482" s="7">
         <v>330</v>
@@ -16465,7 +16500,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F483" s="7">
         <v>330</v>
@@ -16474,10 +16509,10 @@
         <v>101</v>
       </c>
       <c t="s" r="H483" s="8">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c t="s" r="I483" s="7">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c t="s" r="J483" s="7">
         <v>97</v>
@@ -16498,13 +16533,13 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F484" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G484" s="8">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c t="s" r="H484" s="8">
         <v>101</v>
@@ -16513,7 +16548,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -16542,23 +16577,23 @@
         <v>26</v>
       </c>
       <c t="s" r="C486" s="7">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F486" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G486" s="8">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c t="s" r="H486" s="8">
         <v>101</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J486" s="7">
         <v>47</v>
@@ -16581,7 +16616,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F487" s="7">
         <v>330</v>
@@ -16590,10 +16625,10 @@
         <v>101</v>
       </c>
       <c t="s" r="H487" s="8">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c t="s" r="I487" s="7">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c t="s" r="J487" s="7">
         <v>187</v>
@@ -16614,13 +16649,13 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F488" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G488" s="8">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c t="s" r="H488" s="8">
         <v>101</v>
@@ -16629,7 +16664,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J488" s="7">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
@@ -16662,13 +16697,13 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F490" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G490" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="H490" s="8">
         <v>16</v>
@@ -16682,7 +16717,7 @@
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
       <c t="s" r="M490" s="7">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="491" ht="14.25" customHeight="1">
@@ -16697,7 +16732,7 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F491" s="7">
         <v>330</v>
@@ -16706,13 +16741,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H491" s="8">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c t="s" r="I491" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J491" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
@@ -16745,7 +16780,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F493" s="7">
         <v>330</v>
@@ -16765,7 +16800,7 @@
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
       <c t="s" r="M493" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="494" ht="14.25" customHeight="1">
@@ -16780,7 +16815,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F494" s="7">
         <v>330</v>
@@ -16789,7 +16824,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H494" s="8">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c t="s" r="I494" s="7">
         <v>127</v>
@@ -16813,22 +16848,22 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="F495" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G495" s="8">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c t="s" r="H495" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I495" s="7">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
@@ -16861,7 +16896,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F497" s="7">
         <v>330</v>
@@ -16870,10 +16905,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H497" s="8">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c t="s" r="I497" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J497" s="7">
         <v>85</v>
@@ -16894,13 +16929,13 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="F498" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G498" s="8">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c t="s" r="H498" s="8">
         <v>16</v>
@@ -16909,7 +16944,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J498" s="7">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K498" s="7"/>
       <c r="L498" s="7"/>
@@ -16917,7 +16952,7 @@
     </row>
     <row r="499" ht="15.75" customHeight="1">
       <c t="s" r="A499" s="9">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B499" s="9"/>
       <c r="C499" s="9"/>
@@ -16937,7 +16972,7 @@
     <row r="500" ht="66" customHeight="1"/>
     <row r="501" ht="16.5" customHeight="1">
       <c t="s" r="A501" s="10">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B501" s="10"/>
       <c r="C501" s="10"/>
@@ -16950,7 +16985,7 @@
       <c r="J501" s="10"/>
       <c r="K501" s="10"/>
       <c t="s" r="L501" s="11">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="M501" s="11"/>
       <c r="N501" s="11"/>

--- a/Data/FlightPlan/FPL_13AUG26.xlsx
+++ b/Data/FlightPlan/FPL_13AUG26.xlsx
@@ -386,9 +386,6 @@
     <t>14:30</t>
   </si>
   <si>
-    <t>16:52</t>
-  </si>
-  <si>
     <t>18:25</t>
   </si>
   <si>
@@ -467,6 +464,9 @@
     <t>15:30</t>
   </si>
   <si>
+    <t>22:09</t>
+  </si>
+  <si>
     <t>22:45</t>
   </si>
   <si>
@@ -623,6 +623,9 @@
     <t>20:05</t>
   </si>
   <si>
+    <t>20:22</t>
+  </si>
+  <si>
     <t>CAN</t>
   </si>
   <si>
@@ -932,6 +935,9 @@
     <t>16:55</t>
   </si>
   <si>
+    <t>18:24</t>
+  </si>
+  <si>
     <t>07:20</t>
   </si>
   <si>
@@ -992,6 +998,12 @@
     <t>HND</t>
   </si>
   <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
     <t>02:00</t>
   </si>
   <si>
@@ -1043,6 +1055,9 @@
     <t>15:10</t>
   </si>
   <si>
+    <t>16:35</t>
+  </si>
+  <si>
     <t>17:05</t>
   </si>
   <si>
@@ -1109,9 +1124,6 @@
     <t>14:43</t>
   </si>
   <si>
-    <t>16:35</t>
-  </si>
-  <si>
     <t>21:00</t>
   </si>
   <si>
@@ -1148,9 +1160,6 @@
     <t>09:54</t>
   </si>
   <si>
-    <t>17:15</t>
-  </si>
-  <si>
     <t>23:05</t>
   </si>
   <si>
@@ -1172,6 +1181,9 @@
     <t>14:49</t>
   </si>
   <si>
+    <t>17:28</t>
+  </si>
+  <si>
     <t>22:40</t>
   </si>
   <si>
@@ -1193,6 +1205,9 @@
     <t>15:50</t>
   </si>
   <si>
+    <t>16:59</t>
+  </si>
+  <si>
     <t>20:50</t>
   </si>
   <si>
@@ -1247,6 +1262,9 @@
     <t>16:27</t>
   </si>
   <si>
+    <t>17:35</t>
+  </si>
+  <si>
     <t>VN-A648</t>
   </si>
   <si>
@@ -1322,6 +1340,9 @@
     <t>12:28</t>
   </si>
   <si>
+    <t>18:04</t>
+  </si>
+  <si>
     <t>18:35</t>
   </si>
   <si>
@@ -1415,9 +1436,6 @@
     <t>HIJ</t>
   </si>
   <si>
-    <t>00:55</t>
-  </si>
-  <si>
     <t>VN-A667</t>
   </si>
   <si>
@@ -1457,6 +1475,9 @@
     <t>VN-A670</t>
   </si>
   <si>
+    <t>17:02</t>
+  </si>
+  <si>
     <t>VN-A671</t>
   </si>
   <si>
@@ -1496,7 +1517,7 @@
     <t>14:21</t>
   </si>
   <si>
-    <t>16:38</t>
+    <t>16:32</t>
   </si>
   <si>
     <t>DEL</t>
@@ -1511,9 +1532,6 @@
     <t>12:52</t>
   </si>
   <si>
-    <t>17:35</t>
-  </si>
-  <si>
     <t>PKX</t>
   </si>
   <si>
@@ -1634,6 +1652,9 @@
     <t>VN-A698</t>
   </si>
   <si>
+    <t>17:52</t>
+  </si>
+  <si>
     <t>VN-A699</t>
   </si>
   <si>
@@ -1673,6 +1694,9 @@
     <t>UFA</t>
   </si>
   <si>
+    <t>16:56</t>
+  </si>
+  <si>
     <t>VN-A815</t>
   </si>
   <si>
@@ -1703,7 +1727,7 @@
     <t>Total Record(s): 410</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 13, 2026 15:24</t>
+    <t xml:space="preserve">Generated on  Aug 13, 2026 16:02</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3534,7 +3558,7 @@
       </c>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>125</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3561,7 +3585,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c t="s" r="J48" s="7">
         <v>67</v>
@@ -3597,7 +3621,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3624,13 +3648,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H50" s="8">
+        <v>127</v>
+      </c>
+      <c t="s" r="I50" s="7">
         <v>128</v>
       </c>
-      <c t="s" r="I50" s="7">
+      <c t="s" r="J50" s="7">
         <v>129</v>
-      </c>
-      <c t="s" r="J50" s="7">
-        <v>130</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3654,16 +3678,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I51" s="7">
+        <v>130</v>
+      </c>
+      <c t="s" r="J51" s="7">
         <v>131</v>
-      </c>
-      <c t="s" r="J51" s="7">
-        <v>132</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3696,22 +3720,22 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
+        <v>132</v>
+      </c>
+      <c r="F53" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G53" s="8">
         <v>133</v>
       </c>
-      <c r="F53" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G53" s="8">
+      <c t="s" r="H53" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I53" s="7">
         <v>134</v>
       </c>
-      <c t="s" r="H53" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I53" s="7">
+      <c t="s" r="J53" s="7">
         <v>135</v>
-      </c>
-      <c t="s" r="J53" s="7">
-        <v>136</v>
       </c>
       <c r="K53" s="7"/>
       <c r="L53" s="7"/>
@@ -3731,7 +3755,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3743,7 +3767,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="J54" s="7">
         <v>30</v>
@@ -3764,7 +3788,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3776,10 +3800,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I55" s="7">
+        <v>137</v>
+      </c>
+      <c t="s" r="J55" s="7">
         <v>138</v>
-      </c>
-      <c t="s" r="J55" s="7">
-        <v>139</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3797,7 +3821,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3809,13 +3833,13 @@
         <v>74</v>
       </c>
       <c t="s" r="I56" s="7">
+        <v>139</v>
+      </c>
+      <c t="s" r="J56" s="7">
         <v>140</v>
       </c>
-      <c t="s" r="J56" s="7">
+      <c t="s" r="K56" s="7">
         <v>141</v>
-      </c>
-      <c t="s" r="K56" s="7">
-        <v>142</v>
       </c>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
@@ -3849,27 +3873,27 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
+        <v>142</v>
+      </c>
+      <c r="F58" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G58" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H58" s="8">
         <v>143</v>
       </c>
-      <c r="F58" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G58" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H58" s="8">
+      <c t="s" r="I58" s="7">
         <v>144</v>
       </c>
-      <c t="s" r="I58" s="7">
+      <c t="s" r="J58" s="7">
         <v>145</v>
-      </c>
-      <c t="s" r="J58" s="7">
-        <v>146</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3884,27 +3908,27 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
+        <v>142</v>
+      </c>
+      <c r="F59" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G59" s="8">
         <v>143</v>
-      </c>
-      <c r="F59" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G59" s="8">
-        <v>144</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I59" s="7">
+        <v>147</v>
+      </c>
+      <c t="s" r="J59" s="7">
         <v>148</v>
-      </c>
-      <c t="s" r="J59" s="7">
-        <v>149</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c t="s" r="M59" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -3919,7 +3943,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3931,14 +3955,16 @@
         <v>36</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
-      <c r="M60" s="7"/>
+      <c t="s" r="M60" s="7">
+        <v>151</v>
+      </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
       <c t="s" r="A61" s="6">
@@ -3952,7 +3978,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -4198,7 +4224,7 @@
         <v>155</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c t="s" r="J69" s="7">
         <v>161</v>
@@ -4233,7 +4259,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c t="s" r="J70" s="7">
         <v>163</v>
@@ -4337,7 +4363,7 @@
         <v>169</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -4634,7 +4660,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>66</v>
@@ -4902,7 +4928,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I92" s="7">
         <v>195</v>
@@ -4934,7 +4960,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>17</v>
@@ -5021,10 +5047,10 @@
         <v>74</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -5063,7 +5089,9 @@
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
-      <c r="M97" s="7"/>
+      <c t="s" r="M97" s="7">
+        <v>204</v>
+      </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
       <c t="s" r="A98" s="6">
@@ -5086,10 +5114,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H98" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J98" s="7">
         <v>57</v>
@@ -5116,16 +5144,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H99" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5158,7 +5186,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5170,15 +5198,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -5193,7 +5221,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5205,15 +5233,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5228,7 +5256,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5248,7 +5276,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5263,7 +5291,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5283,7 +5311,7 @@
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5298,7 +5326,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5310,7 +5338,7 @@
         <v>190</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>174</v>
@@ -5318,7 +5346,7 @@
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
@@ -5333,7 +5361,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5345,7 +5373,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="J106" s="7">
         <v>24</v>
@@ -5366,7 +5394,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5378,10 +5406,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5399,7 +5427,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5411,10 +5439,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5432,7 +5460,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -5447,7 +5475,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5480,7 +5508,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5492,15 +5520,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5515,7 +5543,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5530,12 +5558,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5550,7 +5578,7 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
@@ -5562,15 +5590,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
       <c t="s" r="M113" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="114" ht="14.25" customHeight="1">
@@ -5600,7 +5628,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5609,18 +5637,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5635,13 +5663,13 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>16</v>
@@ -5650,12 +5678,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5670,7 +5698,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5682,10 +5710,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5718,7 +5746,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5730,15 +5758,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5753,7 +5781,7 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
@@ -5765,7 +5793,7 @@
         <v>171</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>28</v>
@@ -5773,7 +5801,7 @@
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c t="s" r="M120" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" ht="14.25" customHeight="1">
@@ -5788,7 +5816,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5800,7 +5828,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J121" s="7">
         <v>157</v>
@@ -5821,7 +5849,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -5836,7 +5864,7 @@
         <v>33</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5869,13 +5897,13 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>16</v>
@@ -5884,14 +5912,14 @@
         <v>85</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="K124" s="7">
         <v>19</v>
       </c>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5906,7 +5934,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5926,7 +5954,7 @@
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -5941,7 +5969,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5956,7 +5984,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5974,7 +6002,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5986,7 +6014,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>57</v>
@@ -6022,7 +6050,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6037,12 +6065,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c t="s" r="M129" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="130" ht="15" customHeight="1">
@@ -6057,7 +6085,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6069,7 +6097,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>195</v>
@@ -6077,7 +6105,7 @@
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6092,7 +6120,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -6112,7 +6140,7 @@
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c t="s" r="M131" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="132" ht="14.25" customHeight="1">
@@ -6127,7 +6155,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6136,13 +6164,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -6160,13 +6188,13 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>16</v>
@@ -6175,7 +6203,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -6193,7 +6221,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6205,10 +6233,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -6226,7 +6254,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6238,10 +6266,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6274,7 +6302,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6283,10 +6311,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J137" s="7">
         <v>18</v>
@@ -6294,7 +6322,7 @@
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
       <c t="s" r="M137" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="138" ht="14.25" customHeight="1">
@@ -6309,19 +6337,19 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>23</v>
@@ -6329,7 +6357,7 @@
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6344,7 +6372,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6353,20 +6381,20 @@
         <v>27</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>103</v>
       </c>
       <c t="s" r="K139" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -6381,13 +6409,13 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>27</v>
@@ -6396,14 +6424,14 @@
         <v>60</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="K140" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6418,7 +6446,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6427,20 +6455,20 @@
         <v>27</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I141" s="7">
         <v>88</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="K141" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6455,25 +6483,25 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="K142" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
@@ -6492,7 +6520,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6504,7 +6532,7 @@
         <v>115</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>157</v>
@@ -6514,7 +6542,7 @@
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6529,7 +6557,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6547,11 +6575,11 @@
         <v>177</v>
       </c>
       <c t="s" r="K144" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6581,7 +6609,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6593,7 +6621,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>124</v>
@@ -6616,7 +6644,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6628,7 +6656,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>68</v>
@@ -6636,7 +6664,7 @@
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6651,7 +6679,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6660,13 +6688,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6684,22 +6712,22 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="H149" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6732,29 +6760,29 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G151" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H151" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="K151" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6769,7 +6797,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6781,10 +6809,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6817,7 +6845,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6829,15 +6857,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
       <c t="s" r="M154" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -6852,7 +6880,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6861,18 +6889,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H155" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
       <c t="s" r="M155" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
@@ -6887,19 +6915,19 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J156" s="7">
         <v>24</v>
@@ -6907,7 +6935,7 @@
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
       <c t="s" r="M156" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
@@ -6922,7 +6950,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6934,7 +6962,7 @@
         <v>70</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>94</v>
@@ -6970,13 +6998,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>27</v>
@@ -7005,7 +7033,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7020,12 +7048,12 @@
         <v>60</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7040,7 +7068,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7052,7 +7080,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>157</v>
@@ -7073,7 +7101,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7082,13 +7110,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -7121,13 +7149,13 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G164" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H164" s="8">
         <v>46</v>
@@ -7136,12 +7164,12 @@
         <v>18</v>
       </c>
       <c t="s" r="J164" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c t="s" r="M164" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="165" ht="15" customHeight="1">
@@ -7156,7 +7184,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7165,18 +7193,18 @@
         <v>46</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7191,26 +7219,28 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>46</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
-      <c r="M166" s="7"/>
+      <c t="s" r="M166" s="7">
+        <v>308</v>
+      </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
       <c t="s" r="A167" s="6">
@@ -7224,7 +7254,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7239,7 +7269,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -7257,7 +7287,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7266,13 +7296,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>107</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -7305,7 +7335,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7340,7 +7370,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7352,17 +7382,17 @@
         <v>155</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="K171" s="7">
         <v>54</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7377,7 +7407,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -7389,17 +7419,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c t="s" r="K172" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7414,7 +7444,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7423,10 +7453,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>92</v>
@@ -7447,22 +7477,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -7495,7 +7525,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7507,17 +7537,17 @@
         <v>46</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c t="s" r="K176" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L176" s="7"/>
       <c t="s" r="M176" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
@@ -7532,7 +7562,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7544,7 +7574,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J177" s="7">
         <v>117</v>
@@ -7552,7 +7582,7 @@
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
       <c t="s" r="M177" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="178" ht="14.25" customHeight="1">
@@ -7567,7 +7597,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7579,15 +7609,15 @@
         <v>110</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7602,7 +7632,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7617,7 +7647,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7635,7 +7665,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7647,7 +7677,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>34</v>
@@ -7683,7 +7713,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7695,15 +7725,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7718,7 +7748,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7727,17 +7757,21 @@
         <v>16</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="I183" s="7">
         <v>202</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>294</v>
-      </c>
-      <c r="K183" s="7"/>
+        <v>295</v>
+      </c>
+      <c t="s" r="K183" s="7">
+        <v>329</v>
+      </c>
       <c r="L183" s="7"/>
-      <c r="M183" s="7"/>
+      <c t="s" r="M183" s="7">
+        <v>330</v>
+      </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
       <c t="s" r="A184" s="6">
@@ -7751,22 +7785,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7799,7 +7833,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7808,7 +7842,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="I186" s="7">
         <v>20</v>
@@ -7819,7 +7853,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7834,22 +7868,22 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7869,7 +7903,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7881,14 +7915,16 @@
         <v>27</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
-      <c r="M188" s="7"/>
+      <c t="s" r="M188" s="7">
+        <v>56</v>
+      </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
       <c t="s" r="A189" s="6">
@@ -7902,7 +7938,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7935,7 +7971,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7947,10 +7983,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7983,7 +8019,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7992,10 +8028,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>52</v>
@@ -8018,27 +8054,27 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -8053,7 +8089,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -8062,13 +8098,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -8101,7 +8137,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8113,7 +8149,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>85</v>
@@ -8121,7 +8157,7 @@
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8136,7 +8172,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -8148,15 +8184,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8171,7 +8207,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8186,12 +8222,12 @@
         <v>120</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8206,7 +8242,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8218,17 +8254,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="K199" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>235</v>
+        <v>348</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8243,7 +8279,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8255,17 +8291,17 @@
         <v>16</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J200" s="7">
         <v>66</v>
       </c>
       <c t="s" r="K200" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8295,7 +8331,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8307,7 +8343,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>181</v>
@@ -8315,7 +8351,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8330,7 +8366,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8342,10 +8378,10 @@
         <v>155</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -8363,7 +8399,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8378,7 +8414,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8396,7 +8432,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8405,13 +8441,13 @@
         <v>110</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8444,7 +8480,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8456,15 +8492,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8479,7 +8515,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8491,10 +8527,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8514,7 +8550,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8529,12 +8565,12 @@
         <v>52</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8549,7 +8585,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8564,12 +8600,12 @@
         <v>174</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8584,7 +8620,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8593,10 +8629,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>28</v>
@@ -8617,13 +8653,13 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>16</v>
@@ -8650,7 +8686,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8698,7 +8734,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8713,12 +8749,12 @@
         <v>80</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8733,7 +8769,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8745,7 +8781,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>98</v>
@@ -8753,7 +8789,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8768,7 +8804,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8777,10 +8813,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="J217" s="7">
         <v>63</v>
@@ -8788,7 +8824,7 @@
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8803,13 +8839,13 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>16</v>
@@ -8818,12 +8854,12 @@
         <v>124</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -8838,7 +8874,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8847,20 +8883,20 @@
         <v>16</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c t="s" r="K219" s="7">
         <v>24</v>
       </c>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -8875,29 +8911,29 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="K220" s="7">
         <v>41</v>
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8927,7 +8963,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8962,7 +8998,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8977,12 +9013,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8997,7 +9033,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -9009,15 +9045,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -9032,7 +9068,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -9044,15 +9080,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -9067,7 +9103,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9082,14 +9118,14 @@
         <v>88</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="K226" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>366</v>
+        <v>236</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9104,7 +9140,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -9116,13 +9152,13 @@
         <v>27</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c t="s" r="K227" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
@@ -9141,7 +9177,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9156,7 +9192,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -9174,7 +9210,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -9186,7 +9222,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c t="s" r="J229" s="7">
         <v>178</v>
@@ -9222,7 +9258,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9242,7 +9278,7 @@
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9257,7 +9293,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9266,18 +9302,18 @@
         <v>155</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="I232" s="7">
         <v>161</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9292,19 +9328,19 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>155</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c t="s" r="J233" s="7">
         <v>24</v>
@@ -9312,7 +9348,7 @@
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9327,7 +9363,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9360,7 +9396,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9372,10 +9408,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9408,7 +9444,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -9420,7 +9456,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>86</v>
@@ -9428,7 +9464,7 @@
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9443,7 +9479,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9455,7 +9491,7 @@
         <v>50</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>123</v>
@@ -9478,7 +9514,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9490,7 +9526,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>78</v>
@@ -9511,7 +9547,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9520,13 +9556,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9544,22 +9580,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9592,7 +9628,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9601,10 +9637,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J243" s="7">
         <v>163</v>
@@ -9612,7 +9648,7 @@
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9627,26 +9663,28 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
-      <c r="M244" s="7"/>
+      <c t="s" r="M244" s="7">
+        <v>390</v>
+      </c>
     </row>
     <row r="245" ht="15" customHeight="1">
       <c t="s" r="A245" s="6">
@@ -9660,7 +9698,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9672,10 +9710,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="K245" s="7">
         <v>66</v>
@@ -9697,7 +9735,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9719,7 +9757,7 @@
       </c>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9749,7 +9787,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9761,15 +9799,15 @@
         <v>155</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9784,7 +9822,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9796,15 +9834,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9819,7 +9857,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9828,7 +9866,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="I250" s="7">
         <v>119</v>
@@ -9839,7 +9877,7 @@
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c t="s" r="M250" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="251" ht="14.25" customHeight="1">
@@ -9854,27 +9892,27 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G251" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="H251" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c t="s" r="M251" s="7">
-        <v>344</v>
+        <v>398</v>
       </c>
     </row>
     <row r="252" ht="14.25" customHeight="1">
@@ -9889,7 +9927,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9898,13 +9936,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9922,22 +9960,22 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G253" s="8">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="H253" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9970,7 +10008,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9979,18 +10017,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c t="s" r="M255" s="7">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
@@ -10005,13 +10043,13 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G256" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H256" s="8">
         <v>46</v>
@@ -10020,12 +10058,12 @@
         <v>75</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10040,7 +10078,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10055,14 +10093,14 @@
         <v>25</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="K257" s="7">
         <v>124</v>
       </c>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>151</v>
+        <v>202</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10077,7 +10115,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10110,7 +10148,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -10122,10 +10160,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -10143,7 +10181,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10155,7 +10193,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>179</v>
@@ -10191,13 +10229,13 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>27</v>
@@ -10206,12 +10244,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -10226,7 +10264,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10238,15 +10276,15 @@
         <v>46</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -10261,7 +10299,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -10276,12 +10314,12 @@
         <v>124</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>366</v>
+        <v>348</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10296,7 +10334,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -10305,16 +10343,16 @@
         <v>27</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c t="s" r="I265" s="7">
         <v>165</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c t="s" r="K265" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
@@ -10333,29 +10371,29 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c t="s" r="K266" s="7">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10385,7 +10423,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10397,7 +10435,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c t="s" r="J268" s="7">
         <v>19</v>
@@ -10405,7 +10443,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10420,7 +10458,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -10429,18 +10467,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10455,19 +10493,19 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>31</v>
@@ -10488,7 +10526,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -10536,7 +10574,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -10545,10 +10583,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H273" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>195</v>
@@ -10556,7 +10594,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10571,19 +10609,19 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G274" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H274" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>202</v>
@@ -10591,7 +10629,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10606,7 +10644,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10624,11 +10662,11 @@
         <v>78</v>
       </c>
       <c t="s" r="K275" s="7">
-        <v>379</v>
+        <v>417</v>
       </c>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>104</v>
+        <v>41</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10658,7 +10696,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10670,7 +10708,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>117</v>
@@ -10678,7 +10716,7 @@
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10693,7 +10731,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -10713,7 +10751,7 @@
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
       <c t="s" r="M278" s="7">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="279" ht="14.25" customHeight="1">
@@ -10728,7 +10766,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10737,7 +10775,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>38</v>
@@ -10748,7 +10786,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>366</v>
+        <v>348</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10763,13 +10801,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>27</v>
@@ -10778,7 +10816,7 @@
         <v>64</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10792,11 +10830,11 @@
         <v>31</v>
       </c>
       <c t="s" r="C281" s="7">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
@@ -10805,13 +10843,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10844,7 +10882,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10856,15 +10894,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10879,7 +10917,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10894,12 +10932,12 @@
         <v>84</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10914,7 +10952,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10929,12 +10967,12 @@
         <v>54</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10949,7 +10987,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
@@ -10964,7 +11002,7 @@
         <v>202</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10982,7 +11020,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -11015,7 +11053,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -11027,10 +11065,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -11063,7 +11101,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -11072,18 +11110,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11098,19 +11136,19 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>117</v>
@@ -11118,7 +11156,7 @@
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11133,7 +11171,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -11142,10 +11180,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>52</v>
@@ -11155,7 +11193,7 @@
       </c>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11170,29 +11208,29 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c t="s" r="K293" s="7">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11207,7 +11245,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -11216,16 +11254,16 @@
         <v>27</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J294" s="7">
         <v>56</v>
       </c>
       <c t="s" r="K294" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
@@ -11244,29 +11282,29 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="K295" s="7">
         <v>69</v>
       </c>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11281,7 +11319,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
@@ -11290,13 +11328,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c t="s" r="I296" s="7">
         <v>93</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -11329,7 +11367,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -11341,15 +11379,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11364,7 +11402,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -11384,7 +11422,7 @@
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11399,7 +11437,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -11414,12 +11452,12 @@
         <v>59</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11434,7 +11472,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11446,7 +11484,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>161</v>
@@ -11454,7 +11492,7 @@
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11469,7 +11507,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11489,7 +11527,7 @@
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11504,7 +11542,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11522,11 +11560,11 @@
         <v>56</v>
       </c>
       <c t="s" r="K303" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>166</v>
+        <v>443</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11541,7 +11579,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11559,11 +11597,11 @@
         <v>169</v>
       </c>
       <c t="s" r="K304" s="7">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11578,7 +11616,7 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
@@ -11590,13 +11628,13 @@
         <v>27</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="K305" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
@@ -11630,7 +11668,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -11650,7 +11688,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>439</v>
+        <v>446</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11665,7 +11703,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -11677,7 +11715,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c t="s" r="J308" s="7">
         <v>161</v>
@@ -11685,7 +11723,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11700,7 +11738,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -11720,7 +11758,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>440</v>
+        <v>447</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11735,7 +11773,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
@@ -11783,7 +11821,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -11792,18 +11830,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>445</v>
+        <v>452</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11818,19 +11856,19 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c t="s" r="J313" s="7">
         <v>94</v>
@@ -11838,7 +11876,7 @@
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>413</v>
+        <v>419</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11853,7 +11891,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11862,18 +11900,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c t="s" r="I314" s="7">
         <v>100</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11888,27 +11926,27 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>446</v>
+        <v>453</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -11923,7 +11961,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
@@ -11935,15 +11973,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>447</v>
+        <v>454</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -11958,7 +11996,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11967,20 +12005,20 @@
         <v>27</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="K317" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>408</v>
+        <v>56</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11995,25 +12033,25 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>198</v>
       </c>
       <c t="s" r="K318" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
@@ -12032,7 +12070,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -12044,17 +12082,17 @@
         <v>110</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c t="s" r="K319" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>450</v>
+        <v>457</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12069,7 +12107,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12081,17 +12119,17 @@
         <v>27</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="K320" s="7">
         <v>178</v>
       </c>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12121,7 +12159,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -12133,15 +12171,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -12156,7 +12194,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -12168,7 +12206,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>94</v>
@@ -12176,7 +12214,7 @@
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12191,7 +12229,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -12203,15 +12241,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>452</v>
+        <v>459</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12226,7 +12264,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -12246,7 +12284,7 @@
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12261,7 +12299,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -12276,12 +12314,12 @@
         <v>174</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12296,7 +12334,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -12305,16 +12343,16 @@
         <v>46</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>68</v>
       </c>
       <c t="s" r="K327" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
@@ -12333,13 +12371,13 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>16</v>
@@ -12355,7 +12393,7 @@
       </c>
       <c r="L328" s="7"/>
       <c t="s" r="M328" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="329" ht="14.25" customHeight="1">
@@ -12385,7 +12423,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
@@ -12405,7 +12443,7 @@
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>454</v>
+        <v>461</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12420,7 +12458,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -12429,7 +12467,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="I331" s="7">
         <v>75</v>
@@ -12440,7 +12478,7 @@
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
       <c t="s" r="M331" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="332" ht="14.25" customHeight="1">
@@ -12455,13 +12493,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>16</v>
@@ -12470,14 +12508,14 @@
         <v>163</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c t="s" r="K332" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>455</v>
+        <v>462</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12507,7 +12545,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12516,18 +12554,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c t="s" r="I334" s="7">
         <v>98</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>458</v>
+        <v>465</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12542,13 +12580,13 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>16</v>
@@ -12562,7 +12600,7 @@
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>459</v>
+        <v>466</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12577,7 +12615,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -12586,17 +12624,19 @@
         <v>16</v>
       </c>
       <c t="s" r="H336" s="8">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
-      <c r="M336" s="7"/>
+      <c t="s" r="M336" s="7">
+        <v>409</v>
+      </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
       <c t="s" r="A337" s="6">
@@ -12610,19 +12650,19 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
+        <v>463</v>
+      </c>
+      <c r="F337" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G337" s="8">
+        <v>303</v>
+      </c>
+      <c t="s" r="H337" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I337" s="7">
         <v>456</v>
-      </c>
-      <c r="F337" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G337" s="8">
-        <v>302</v>
-      </c>
-      <c t="s" r="H337" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="I337" s="7">
-        <v>449</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>31</v>
@@ -12658,7 +12698,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12670,7 +12710,7 @@
         <v>96</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>84</v>
@@ -12693,7 +12733,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12713,7 +12753,7 @@
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>461</v>
+        <v>468</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12728,7 +12768,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12763,7 +12803,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12772,18 +12812,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="I342" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -12798,13 +12838,13 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>27</v>
@@ -12846,7 +12886,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12858,15 +12898,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>463</v>
+        <v>470</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12881,7 +12921,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12896,12 +12936,12 @@
         <v>86</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>464</v>
+        <v>471</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12916,7 +12956,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12925,18 +12965,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="I347" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>465</v>
+        <v>472</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -12951,13 +12991,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>27</v>
@@ -12966,12 +13006,12 @@
         <v>88</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -12986,7 +13026,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12995,10 +13035,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>198</v>
@@ -13019,22 +13059,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -13067,7 +13107,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -13076,13 +13116,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c t="s" r="I352" s="7">
         <v>159</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -13102,13 +13142,13 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>27</v>
@@ -13117,12 +13157,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13137,7 +13177,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -13149,7 +13189,7 @@
         <v>46</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>198</v>
@@ -13170,7 +13210,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
@@ -13185,7 +13225,7 @@
         <v>67</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -13203,7 +13243,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -13218,7 +13258,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>468</v>
+        <v>330</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -13251,7 +13291,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -13260,10 +13300,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>97</v>
@@ -13271,7 +13311,7 @@
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
       <c t="s" r="M358" s="7">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="359" ht="14.25" customHeight="1">
@@ -13286,27 +13326,27 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13321,27 +13361,27 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13356,19 +13396,19 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>52</v>
@@ -13376,7 +13416,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13391,7 +13431,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13400,18 +13440,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13426,13 +13466,13 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>16</v>
@@ -13459,7 +13499,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -13471,10 +13511,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13492,7 +13532,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13507,7 +13547,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -13540,7 +13580,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F367" s="7">
         <v>320</v>
@@ -13552,7 +13592,7 @@
         <v>167</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>85</v>
@@ -13560,7 +13600,7 @@
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
       <c t="s" r="M367" s="7">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="368" ht="14.25" customHeight="1">
@@ -13575,7 +13615,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F368" s="7">
         <v>320</v>
@@ -13587,15 +13627,15 @@
         <v>16</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13610,7 +13650,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F369" s="7">
         <v>320</v>
@@ -13625,12 +13665,12 @@
         <v>116</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
       <c t="s" r="M369" s="7">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -13645,7 +13685,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F370" s="7">
         <v>320</v>
@@ -13665,7 +13705,7 @@
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
       <c t="s" r="M370" s="7">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="371" ht="14.25" customHeight="1">
@@ -13680,7 +13720,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F371" s="7">
         <v>320</v>
@@ -13689,13 +13729,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13713,22 +13753,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13761,7 +13801,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -13773,7 +13813,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>117</v>
@@ -13781,7 +13821,7 @@
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -13796,7 +13836,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -13816,7 +13856,7 @@
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
       <c t="s" r="M375" s="7">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="376" ht="14.25" customHeight="1">
@@ -13831,7 +13871,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -13840,7 +13880,7 @@
         <v>16</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c t="s" r="I376" s="7">
         <v>91</v>
@@ -13850,7 +13890,9 @@
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
-      <c r="M376" s="7"/>
+      <c t="s" r="M376" s="7">
+        <v>24</v>
+      </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
       <c t="s" r="A377" s="6">
@@ -13864,22 +13906,22 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13897,7 +13939,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
@@ -13909,10 +13951,10 @@
         <v>115</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13930,7 +13972,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13942,10 +13984,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13978,25 +14020,25 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J381" s="7">
         <v>191</v>
       </c>
       <c t="s" r="K381" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L381" s="7"/>
       <c t="s" r="M381" s="7">
@@ -14015,7 +14057,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -14024,10 +14066,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H382" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>38</v>
@@ -14050,26 +14092,28 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F383" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G383" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="H383" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
-      <c r="M383" s="7"/>
+      <c t="s" r="M383" s="7">
+        <v>488</v>
+      </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
       <c t="s" r="A384" s="6">
@@ -14083,7 +14127,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14098,7 +14142,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -14116,7 +14160,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14149,7 +14193,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -14161,7 +14205,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>178</v>
@@ -14197,7 +14241,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -14206,18 +14250,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>485</v>
+        <v>492</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14232,19 +14276,19 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J389" s="7">
         <v>52</v>
@@ -14252,7 +14296,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14267,7 +14311,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="F390" s="7">
         <v>320</v>
@@ -14276,18 +14320,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H390" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14302,19 +14346,19 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="F391" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G391" s="8">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c t="s" r="H391" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c t="s" r="J391" s="7">
         <v>56</v>
@@ -14335,7 +14379,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="F392" s="7">
         <v>320</v>
@@ -14344,10 +14388,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>185</v>
@@ -14368,19 +14412,19 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="F393" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="J393" s="7">
         <v>178</v>
@@ -14416,13 +14460,13 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F395" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>27</v>
@@ -14431,12 +14475,12 @@
         <v>25</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14451,7 +14495,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -14463,14 +14507,16 @@
         <v>190</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
-      <c r="M396" s="7"/>
+      <c t="s" r="M396" s="7">
+        <v>166</v>
+      </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
       <c t="s" r="A397" s="6">
@@ -14484,7 +14530,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -14499,7 +14545,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -14517,7 +14563,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -14532,7 +14578,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14565,7 +14611,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
@@ -14580,12 +14626,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
       <c t="s" r="M400" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="401" ht="14.25" customHeight="1">
@@ -14600,7 +14646,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F401" s="7">
         <v>321</v>
@@ -14612,7 +14658,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>101</v>
@@ -14635,7 +14681,7 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F402" s="7">
         <v>321</v>
@@ -14644,18 +14690,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>489</v>
+        <v>496</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14670,19 +14716,19 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F403" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H403" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J403" s="7">
         <v>78</v>
@@ -14703,7 +14749,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F404" s="7">
         <v>321</v>
@@ -14712,13 +14758,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14736,22 +14782,22 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="F405" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14784,7 +14830,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="F407" s="7">
         <v>321</v>
@@ -14804,7 +14850,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>493</v>
+        <v>500</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14819,7 +14865,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="F408" s="7">
         <v>321</v>
@@ -14839,7 +14885,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14854,7 +14900,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="F409" s="7">
         <v>321</v>
@@ -14874,7 +14920,7 @@
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>495</v>
+        <v>502</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -14889,7 +14935,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -14898,13 +14944,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H410" s="8">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c t="s" r="I410" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14922,22 +14968,22 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14970,7 +15016,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F413" s="7">
         <v>320</v>
@@ -14985,12 +15031,12 @@
         <v>97</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15005,7 +15051,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F414" s="7">
         <v>320</v>
@@ -15017,15 +15063,15 @@
         <v>190</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>499</v>
+        <v>506</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -15040,7 +15086,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F415" s="7">
         <v>320</v>
@@ -15055,14 +15101,14 @@
         <v>52</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c t="s" r="K415" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15077,7 +15123,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F416" s="7">
         <v>320</v>
@@ -15089,17 +15135,17 @@
         <v>115</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="K416" s="7">
         <v>165</v>
       </c>
       <c r="L416" s="7"/>
       <c t="s" r="M416" s="7">
-        <v>500</v>
+        <v>417</v>
       </c>
     </row>
     <row r="417" ht="14.25" customHeight="1">
@@ -15114,7 +15160,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F417" s="7">
         <v>320</v>
@@ -15126,17 +15172,17 @@
         <v>27</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="K417" s="7">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="L417" s="7"/>
       <c t="s" r="M417" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
@@ -15151,7 +15197,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F418" s="7">
         <v>320</v>
@@ -15160,20 +15206,20 @@
         <v>27</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="K418" s="7">
         <v>69</v>
       </c>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15188,13 +15234,13 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F419" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>27</v>
@@ -15203,14 +15249,14 @@
         <v>71</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c t="s" r="K419" s="7">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="L419" s="7"/>
       <c t="s" r="M419" s="7">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="420" ht="15" customHeight="1">
@@ -15240,7 +15286,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F421" s="7">
         <v>320</v>
@@ -15252,15 +15298,15 @@
         <v>190</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="422" ht="14.25" customHeight="1">
@@ -15275,7 +15321,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -15295,7 +15341,7 @@
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
       <c t="s" r="M422" s="7">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="423" ht="14.25" customHeight="1">
@@ -15310,7 +15356,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -15319,10 +15365,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H423" s="8">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J423" s="7">
         <v>64</v>
@@ -15330,7 +15376,7 @@
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
       <c t="s" r="M423" s="7">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="424" ht="14.25" customHeight="1">
@@ -15345,13 +15391,13 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G424" s="8">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c t="s" r="H424" s="8">
         <v>27</v>
@@ -15378,7 +15424,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -15387,13 +15433,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H425" s="8">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c t="s" r="I425" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J425" s="7">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="K425" s="7"/>
       <c r="L425" s="7"/>
@@ -15411,22 +15457,22 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G426" s="8">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c t="s" r="H426" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c t="s" r="J426" s="7">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="K426" s="7"/>
       <c r="L426" s="7"/>
@@ -15459,7 +15505,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F428" s="7">
         <v>321</v>
@@ -15471,15 +15517,15 @@
         <v>171</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
       <c t="s" r="M428" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="429" ht="14.25" customHeight="1">
@@ -15494,7 +15540,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F429" s="7">
         <v>321</v>
@@ -15509,12 +15555,12 @@
         <v>123</v>
       </c>
       <c t="s" r="J429" s="7">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K429" s="7"/>
       <c r="L429" s="7"/>
       <c t="s" r="M429" s="7">
-        <v>517</v>
+        <v>523</v>
       </c>
     </row>
     <row r="430" ht="15" customHeight="1">
@@ -15529,7 +15575,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F430" s="7">
         <v>321</v>
@@ -15541,10 +15587,10 @@
         <v>46</v>
       </c>
       <c t="s" r="I430" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J430" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K430" s="7"/>
       <c r="L430" s="7"/>
@@ -15562,7 +15608,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F431" s="7">
         <v>321</v>
@@ -15574,7 +15620,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I431" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c t="s" r="J431" s="7">
         <v>152</v>
@@ -15595,7 +15641,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="F432" s="7">
         <v>321</v>
@@ -15604,13 +15650,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H432" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I432" s="7">
         <v>107</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -15643,7 +15689,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -15652,18 +15698,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H434" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="I434" s="7">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
       <c t="s" r="M434" s="7">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="435" ht="15" customHeight="1">
@@ -15678,19 +15724,19 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G435" s="8">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="H435" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I435" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J435" s="7">
         <v>166</v>
@@ -15698,7 +15744,7 @@
       <c r="K435" s="7"/>
       <c r="L435" s="7"/>
       <c t="s" r="M435" s="7">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="436" ht="14.25" customHeight="1">
@@ -15713,22 +15759,22 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
+        <v>524</v>
+      </c>
+      <c r="F436" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G436" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H436" s="8">
         <v>518</v>
       </c>
-      <c r="F436" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G436" s="8">
-        <v>16</v>
-      </c>
-      <c t="s" r="H436" s="8">
-        <v>512</v>
-      </c>
       <c t="s" r="I436" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c t="s" r="J436" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K436" s="7"/>
       <c r="L436" s="7"/>
@@ -15746,22 +15792,22 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
+        <v>524</v>
+      </c>
+      <c r="F437" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G437" s="8">
         <v>518</v>
       </c>
-      <c r="F437" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G437" s="8">
-        <v>512</v>
-      </c>
       <c t="s" r="H437" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I437" s="7">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c t="s" r="J437" s="7">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="K437" s="7"/>
       <c r="L437" s="7"/>
@@ -15794,7 +15840,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -15814,7 +15860,7 @@
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
       <c t="s" r="M439" s="7">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="440" ht="15" customHeight="1">
@@ -15829,7 +15875,7 @@
       </c>
       <c r="D440" s="7"/>
       <c t="s" r="E440" s="7">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F440" s="7">
         <v>321</v>
@@ -15838,10 +15884,10 @@
         <v>155</v>
       </c>
       <c t="s" r="H440" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I440" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J440" s="7">
         <v>61</v>
@@ -15849,7 +15895,7 @@
       <c r="K440" s="7"/>
       <c r="L440" s="7"/>
       <c t="s" r="M440" s="7">
-        <v>525</v>
+        <v>531</v>
       </c>
     </row>
     <row r="441" ht="14.25" customHeight="1">
@@ -15864,13 +15910,13 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G441" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H441" s="8">
         <v>155</v>
@@ -15884,7 +15930,7 @@
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
       <c t="s" r="M441" s="7">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="442" ht="14.25" customHeight="1">
@@ -15899,7 +15945,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -15911,17 +15957,17 @@
         <v>190</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c t="s" r="J442" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c t="s" r="K442" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="L442" s="7"/>
       <c t="s" r="M442" s="7">
-        <v>408</v>
+        <v>183</v>
       </c>
     </row>
     <row r="443" ht="14.25" customHeight="1">
@@ -15936,7 +15982,7 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
@@ -15951,7 +15997,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -15969,7 +16015,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -15981,7 +16027,7 @@
         <v>36</v>
       </c>
       <c t="s" r="I444" s="7">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c t="s" r="J444" s="7">
         <v>159</v>
@@ -16017,7 +16063,7 @@
       </c>
       <c r="D446" s="7"/>
       <c t="s" r="E446" s="7">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F446" s="7">
         <v>321</v>
@@ -16026,10 +16072,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H446" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="I446" s="7">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c t="s" r="J446" s="7">
         <v>172</v>
@@ -16037,7 +16083,7 @@
       <c r="K446" s="7"/>
       <c r="L446" s="7"/>
       <c t="s" r="M446" s="7">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="447" ht="14.25" customHeight="1">
@@ -16052,13 +16098,13 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G447" s="8">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="H447" s="8">
         <v>16</v>
@@ -16067,12 +16113,12 @@
         <v>34</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K447" s="7"/>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="448" ht="14.25" customHeight="1">
@@ -16087,7 +16133,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -16096,18 +16142,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H448" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="I448" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="J448" s="7">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="K448" s="7"/>
       <c r="L448" s="7"/>
       <c t="s" r="M448" s="7">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="449" ht="14.25" customHeight="1">
@@ -16122,13 +16168,13 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G449" s="8">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c t="s" r="H449" s="8">
         <v>16</v>
@@ -16137,12 +16183,12 @@
         <v>87</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
       <c t="s" r="M449" s="7">
-        <v>533</v>
+        <v>539</v>
       </c>
     </row>
     <row r="450" ht="15" customHeight="1">
@@ -16157,7 +16203,7 @@
       </c>
       <c r="D450" s="7"/>
       <c t="s" r="E450" s="7">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F450" s="7">
         <v>321</v>
@@ -16190,7 +16236,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
@@ -16202,7 +16248,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I451" s="7">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c t="s" r="J451" s="7">
         <v>41</v>
@@ -16223,7 +16269,7 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F452" s="7">
         <v>321</v>
@@ -16232,13 +16278,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H452" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="I452" s="7">
         <v>69</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -16256,19 +16302,19 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="F453" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G453" s="8">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c t="s" r="H453" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I453" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c t="s" r="J453" s="7">
         <v>107</v>
@@ -16304,7 +16350,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F455" s="7">
         <v>320</v>
@@ -16319,12 +16365,12 @@
         <v>98</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
       <c t="s" r="M455" s="7">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="456" ht="14.25" customHeight="1">
@@ -16339,7 +16385,7 @@
       </c>
       <c r="D456" s="7"/>
       <c t="s" r="E456" s="7">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F456" s="7">
         <v>320</v>
@@ -16351,10 +16397,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I456" s="7">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c t="s" r="J456" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K456" s="7"/>
       <c r="L456" s="7"/>
@@ -16374,7 +16420,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -16383,18 +16429,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H457" s="8">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c t="s" r="I457" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
       <c t="s" r="M457" s="7">
-        <v>537</v>
+        <v>543</v>
       </c>
     </row>
     <row r="458" ht="14.25" customHeight="1">
@@ -16409,13 +16455,13 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G458" s="8">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c t="s" r="H458" s="8">
         <v>16</v>
@@ -16424,7 +16470,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J458" s="7">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K458" s="7"/>
       <c r="L458" s="7"/>
@@ -16442,7 +16488,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
@@ -16451,13 +16497,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H459" s="8">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c t="s" r="I459" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J459" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K459" s="7"/>
       <c r="L459" s="7"/>
@@ -16475,13 +16521,13 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F460" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G460" s="8">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c t="s" r="H460" s="8">
         <v>16</v>
@@ -16490,7 +16536,7 @@
         <v>71</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -16523,7 +16569,7 @@
       </c>
       <c r="D462" s="7"/>
       <c t="s" r="E462" s="7">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F462" s="7">
         <v>321</v>
@@ -16535,7 +16581,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I462" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J462" s="7">
         <v>51</v>
@@ -16543,7 +16589,7 @@
       <c r="K462" s="7"/>
       <c r="L462" s="7"/>
       <c t="s" r="M462" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="463" ht="14.25" customHeight="1">
@@ -16558,7 +16604,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -16567,18 +16613,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="I463" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J463" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="K463" s="7"/>
       <c r="L463" s="7"/>
       <c t="s" r="M463" s="7">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="464" ht="14.25" customHeight="1">
@@ -16593,13 +16639,13 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>27</v>
@@ -16613,7 +16659,7 @@
       <c r="K464" s="7"/>
       <c r="L464" s="7"/>
       <c t="s" r="M464" s="7">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="465" ht="15" customHeight="1">
@@ -16628,7 +16674,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -16640,10 +16686,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I465" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
@@ -16676,7 +16722,7 @@
       </c>
       <c r="D467" s="7"/>
       <c t="s" r="E467" s="7">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="F467" s="7">
         <v>321</v>
@@ -16694,11 +16740,11 @@
         <v>124</v>
       </c>
       <c t="s" r="K467" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L467" s="7"/>
       <c t="s" r="M467" s="7">
-        <v>500</v>
+        <v>547</v>
       </c>
     </row>
     <row r="468" ht="14.25" customHeight="1">
@@ -16713,7 +16759,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -16746,7 +16792,7 @@
       </c>
       <c r="D469" s="7"/>
       <c t="s" r="E469" s="7">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="F469" s="7">
         <v>321</v>
@@ -16761,7 +16807,7 @@
         <v>157</v>
       </c>
       <c t="s" r="J469" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="K469" s="7"/>
       <c r="L469" s="7"/>
@@ -16794,7 +16840,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F471" s="7">
         <v>320</v>
@@ -16806,7 +16852,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>98</v>
@@ -16814,7 +16860,7 @@
       <c r="K471" s="7"/>
       <c r="L471" s="7"/>
       <c t="s" r="M471" s="7">
-        <v>542</v>
+        <v>549</v>
       </c>
     </row>
     <row r="472" ht="14.25" customHeight="1">
@@ -16829,7 +16875,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F472" s="7">
         <v>320</v>
@@ -16844,14 +16890,14 @@
         <v>59</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="K472" s="7">
         <v>59</v>
       </c>
       <c r="L472" s="7"/>
       <c t="s" r="M472" s="7">
-        <v>543</v>
+        <v>550</v>
       </c>
     </row>
     <row r="473" ht="14.25" customHeight="1">
@@ -16866,7 +16912,7 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F473" s="7">
         <v>320</v>
@@ -16878,7 +16924,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I473" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J473" s="7">
         <v>63</v>
@@ -16886,7 +16932,7 @@
       <c r="K473" s="7"/>
       <c r="L473" s="7"/>
       <c t="s" r="M473" s="7">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="474" ht="14.25" customHeight="1">
@@ -16901,7 +16947,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F474" s="7">
         <v>320</v>
@@ -16916,12 +16962,12 @@
         <v>122</v>
       </c>
       <c t="s" r="J474" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K474" s="7"/>
       <c r="L474" s="7"/>
       <c t="s" r="M474" s="7">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="475" ht="15" customHeight="1">
@@ -16936,7 +16982,7 @@
       </c>
       <c r="D475" s="7"/>
       <c t="s" r="E475" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F475" s="7">
         <v>320</v>
@@ -16948,7 +16994,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I475" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c t="s" r="J475" s="7">
         <v>28</v>
@@ -16969,7 +17015,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>541</v>
+        <v>548</v>
       </c>
       <c r="F476" s="7">
         <v>320</v>
@@ -17017,7 +17063,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F478" s="7">
         <v>330</v>
@@ -17029,7 +17075,7 @@
         <v>110</v>
       </c>
       <c t="s" r="I478" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J478" s="7">
         <v>181</v>
@@ -17052,7 +17098,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F479" s="7">
         <v>330</v>
@@ -17061,20 +17107,20 @@
         <v>110</v>
       </c>
       <c t="s" r="H479" s="8">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c t="s" r="K479" s="7">
         <v>63</v>
       </c>
       <c r="L479" s="7"/>
       <c t="s" r="M479" s="7">
-        <v>546</v>
+        <v>553</v>
       </c>
     </row>
     <row r="480" ht="15" customHeight="1">
@@ -17089,29 +17135,29 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>544</v>
+        <v>551</v>
       </c>
       <c r="F480" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G480" s="8">
-        <v>545</v>
+        <v>552</v>
       </c>
       <c t="s" r="H480" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I480" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c t="s" r="K480" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L480" s="7"/>
       <c t="s" r="M480" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="481" ht="14.25" customHeight="1">
@@ -17141,7 +17187,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="F482" s="7">
         <v>330</v>
@@ -17156,7 +17202,7 @@
         <v>116</v>
       </c>
       <c t="s" r="J482" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
@@ -17176,7 +17222,7 @@
       </c>
       <c r="D483" s="7"/>
       <c t="s" r="E483" s="7">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="F483" s="7">
         <v>330</v>
@@ -17185,10 +17231,10 @@
         <v>110</v>
       </c>
       <c t="s" r="H483" s="8">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c t="s" r="I483" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J483" s="7">
         <v>106</v>
@@ -17196,7 +17242,7 @@
       <c r="K483" s="7"/>
       <c r="L483" s="7"/>
       <c t="s" r="M483" s="7">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="484" ht="14.25" customHeight="1">
@@ -17211,13 +17257,13 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>547</v>
+        <v>554</v>
       </c>
       <c r="F484" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G484" s="8">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c t="s" r="H484" s="8">
         <v>110</v>
@@ -17226,7 +17272,7 @@
         <v>152</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -17255,23 +17301,23 @@
         <v>26</v>
       </c>
       <c t="s" r="C486" s="7">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F486" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G486" s="8">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c t="s" r="H486" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I486" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="J486" s="7">
         <v>48</v>
@@ -17294,7 +17340,7 @@
       </c>
       <c r="D487" s="7"/>
       <c t="s" r="E487" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F487" s="7">
         <v>330</v>
@@ -17303,10 +17349,10 @@
         <v>110</v>
       </c>
       <c t="s" r="H487" s="8">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c t="s" r="I487" s="7">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c t="s" r="J487" s="7">
         <v>202</v>
@@ -17314,7 +17360,7 @@
       <c r="K487" s="7"/>
       <c r="L487" s="7"/>
       <c t="s" r="M487" s="7">
-        <v>306</v>
+        <v>561</v>
       </c>
     </row>
     <row r="488" ht="14.25" customHeight="1">
@@ -17329,22 +17375,22 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="F488" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G488" s="8">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c t="s" r="H488" s="8">
         <v>110</v>
       </c>
       <c t="s" r="I488" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J488" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K488" s="7"/>
       <c r="L488" s="7"/>
@@ -17377,19 +17423,19 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="F490" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G490" s="8">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c t="s" r="H490" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I490" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c t="s" r="J490" s="7">
         <v>176</v>
@@ -17397,7 +17443,7 @@
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
       <c t="s" r="M490" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="491" ht="14.25" customHeight="1">
@@ -17412,7 +17458,7 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>554</v>
+        <v>562</v>
       </c>
       <c r="F491" s="7">
         <v>330</v>
@@ -17421,13 +17467,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H491" s="8">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c t="s" r="I491" s="7">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c t="s" r="J491" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K491" s="7"/>
       <c r="L491" s="7"/>
@@ -17460,7 +17506,7 @@
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="F493" s="7">
         <v>330</v>
@@ -17475,12 +17521,12 @@
         <v>48</v>
       </c>
       <c t="s" r="J493" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
       <c t="s" r="M493" s="7">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="494" ht="14.25" customHeight="1">
@@ -17495,7 +17541,7 @@
       </c>
       <c r="D494" s="7"/>
       <c t="s" r="E494" s="7">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="F494" s="7">
         <v>330</v>
@@ -17504,18 +17550,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H494" s="8">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c t="s" r="I494" s="7">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c t="s" r="J494" s="7">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="K494" s="7"/>
       <c r="L494" s="7"/>
       <c t="s" r="M494" s="7">
-        <v>558</v>
+        <v>566</v>
       </c>
     </row>
     <row r="495" ht="15" customHeight="1">
@@ -17530,22 +17576,22 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>556</v>
+        <v>564</v>
       </c>
       <c r="F495" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G495" s="8">
-        <v>557</v>
+        <v>565</v>
       </c>
       <c t="s" r="H495" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I495" s="7">
-        <v>559</v>
+        <v>567</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
@@ -17578,7 +17624,7 @@
       </c>
       <c r="D497" s="7"/>
       <c t="s" r="E497" s="7">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F497" s="7">
         <v>330</v>
@@ -17587,10 +17633,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H497" s="8">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c t="s" r="I497" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J497" s="7">
         <v>92</v>
@@ -17598,7 +17644,7 @@
       <c r="K497" s="7"/>
       <c r="L497" s="7"/>
       <c t="s" r="M497" s="7">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="498" ht="14.25" customHeight="1">
@@ -17613,13 +17659,13 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>560</v>
+        <v>568</v>
       </c>
       <c r="F498" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G498" s="8">
-        <v>561</v>
+        <v>569</v>
       </c>
       <c t="s" r="H498" s="8">
         <v>16</v>
@@ -17628,7 +17674,7 @@
         <v>107</v>
       </c>
       <c t="s" r="J498" s="7">
-        <v>562</v>
+        <v>570</v>
       </c>
       <c r="K498" s="7"/>
       <c r="L498" s="7"/>
@@ -17636,7 +17682,7 @@
     </row>
     <row r="499" ht="15.75" customHeight="1">
       <c t="s" r="A499" s="9">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="B499" s="9"/>
       <c r="C499" s="9"/>
@@ -17656,7 +17702,7 @@
     <row r="500" ht="66" customHeight="1"/>
     <row r="501" ht="16.5" customHeight="1">
       <c t="s" r="A501" s="10">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="B501" s="10"/>
       <c r="C501" s="10"/>
@@ -17669,7 +17715,7 @@
       <c r="J501" s="10"/>
       <c r="K501" s="10"/>
       <c t="s" r="L501" s="11">
-        <v>565</v>
+        <v>573</v>
       </c>
       <c r="M501" s="11"/>
       <c r="N501" s="11"/>
